--- a/Templates/tabulatedValuesTemplate.xlsx
+++ b/Templates/tabulatedValuesTemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailmissouri-my.sharepoint.com/personal/arvkb9_umsystem_edu/Documents/896 - B.S Aerospace Engineering Courses/92 - Fall 2026/6 - AE4780-Meeks/Github Repo/AE4780-Meeks/Templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8331AD9-2580-4981-A1BF-8B38E094E228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{C8331AD9-2580-4981-A1BF-8B38E094E228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA1295AE-C5F2-4D75-A5F1-DF1AC3CCD71A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1B61AF13-B459-4C3D-BF8D-2C9191432F03}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{1B61AF13-B459-4C3D-BF8D-2C9191432F03}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="2" r:id="rId1"/>
@@ -49,7 +49,7 @@
   </si>
   <si>
     <t>This file, specifically the "Example" sheet, contains an example config. for storing tabulated values for a dependent variable. This is meant to be used with a data.txt config. file where a value for a variable in a given config. is set to "&lt;filename&gt;" where &lt;filename&gt; is replaced with the name of the .xlsx file where that variable's tabulated values are stored for one (1) or more independent variables. An example would be if you have a propellant_data.txt config. file, and one config. doesn't have a set value for some variable "c_p", for example, and instead the line is set to "tabulated". Then in one of these tabulated values .xslx files one would store the independent variable values in the first group of columns, with the first row as labels for those columns, and the dependent variable values in the last column, with the first row's cell being a label for that column.
-Check the "Example" sheet to see an example. In an actual file, do not include a "README" sheet, and do not change the default sheet name.</t>
+Check the "Example" sheet to see an example. In an actual file, do not have any extra sheets besides the one with the data</t>
   </si>
 </sst>
 </file>
@@ -89,7 +89,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,10 +425,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29F3914A-5B88-470C-91D4-D6F5BA1F2971}">
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -439,7 +439,7 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -448,7 +448,7 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -457,7 +457,7 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -466,7 +466,7 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -475,7 +475,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -484,7 +484,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -493,7 +493,7 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -502,7 +502,7 @@
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -511,7 +511,7 @@
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -520,7 +520,7 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -529,7 +529,7 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -538,7 +538,7 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -547,7 +547,7 @@
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -556,9 +556,18 @@
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
     </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G14"/>
+    <mergeCell ref="A1:G15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -567,13 +576,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13D3E5AF-311B-4C50-812A-35B87D33C5EC}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -581,7 +590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>90</v>
       </c>
@@ -589,7 +598,7 @@
         <v>500000000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>100</v>
       </c>
@@ -597,7 +606,7 @@
         <v>450000000</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>110</v>
       </c>
@@ -605,7 +614,7 @@
         <v>400000000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>120</v>
       </c>
@@ -613,7 +622,7 @@
         <v>350000000</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>130</v>
       </c>
@@ -621,7 +630,7 @@
         <v>300000000</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>140</v>
       </c>
@@ -629,7 +638,7 @@
         <v>250000000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>150</v>
       </c>
@@ -637,7 +646,7 @@
         <v>200000000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>160</v>
       </c>
@@ -645,7 +654,7 @@
         <v>180000000</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>170</v>
       </c>
@@ -653,7 +662,7 @@
         <v>160000000</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>180</v>
       </c>
